--- a/Dev_GNC/TableData/TextDataTable.xlsx
+++ b/Dev_GNC/TableData/TextDataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProjects\CardGame\CardGameTable\Table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4122718F-07FC-4ECF-BA6A-48E38D078CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A40A66-ABA9-4394-9F77-1CA91F837AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextData" sheetId="1" r:id="rId1"/>
@@ -496,10 +496,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>text_pawn_name_assult</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>text_pawn_name_heavy</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -630,6 +626,10 @@
   </si>
   <si>
     <t>Heavy Armor</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_pawn_name_assault</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -945,7 +945,7 @@
     <col min="2" max="2" width="26.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -962,7 +962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -976,7 +976,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -990,7 +990,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>155</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
@@ -1348,10 +1348,10 @@
         <v>156</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
@@ -1359,13 +1359,13 @@
         <v>103</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
@@ -1373,13 +1373,13 @@
         <v>104</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
@@ -1387,13 +1387,13 @@
         <v>105</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
@@ -1407,7 +1407,7 @@
         <v>84</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
@@ -1421,7 +1421,7 @@
         <v>86</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
@@ -1435,7 +1435,7 @@
         <v>88</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
@@ -1449,7 +1449,7 @@
         <v>90</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
@@ -1463,7 +1463,7 @@
         <v>92</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>93</v>
@@ -1480,7 +1480,7 @@
         <v>95</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
@@ -1494,7 +1494,7 @@
         <v>97</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
@@ -1508,7 +1508,7 @@
         <v>99</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
@@ -1522,7 +1522,7 @@
         <v>101</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
@@ -1536,7 +1536,7 @@
         <v>103</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
@@ -1550,7 +1550,7 @@
         <v>105</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
@@ -1564,10 +1564,10 @@
         <v>107</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>2001</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>2002</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>2003</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>2004</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>2005</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>2006</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>2007</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>2008</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>2009</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>2010</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>2011</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>131</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1713,7 +1713,7 @@
         <v>133</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1727,7 +1727,7 @@
         <v>135</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1741,7 +1741,7 @@
         <v>137</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1755,7 +1755,7 @@
         <v>139</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1769,7 +1769,7 @@
         <v>141</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1783,7 +1783,7 @@
         <v>143</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1797,7 +1797,7 @@
         <v>90</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1811,7 +1811,7 @@
         <v>92</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1825,7 +1825,7 @@
         <v>95</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1833,13 +1833,13 @@
         <v>3011</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1853,7 +1853,7 @@
         <v>99</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1867,7 +1867,7 @@
         <v>101</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1881,7 +1881,7 @@
         <v>103</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1895,7 +1895,7 @@
         <v>151</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -1909,7 +1909,7 @@
         <v>153</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
